--- a/Result/profitability/6223.xlsx
+++ b/Result/profitability/6223.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>7.7075</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>54.7875</v>
+        <v>54.9975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>7.01125</v>
+        <v>8.00625</v>
       </c>
       <c r="N3" t="n">
-        <v>53.055</v>
+        <v>53.325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>6.135</v>
+        <v>7.11875</v>
       </c>
       <c r="N4" t="n">
-        <v>50.625</v>
+        <v>50.7475</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.85</v>
       </c>
       <c r="M5" t="n">
-        <v>5.28125</v>
+        <v>6.39125</v>
       </c>
       <c r="N5" t="n">
-        <v>47.975</v>
+        <v>47.98500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3925</v>
+        <v>5.173749999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>44.11</v>
+        <v>44.73375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.895</v>
       </c>
       <c r="N7" t="n">
-        <v>41.79875</v>
+        <v>42.3725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.97625</v>
+        <v>2.35375</v>
       </c>
       <c r="N8" t="n">
-        <v>39.34375</v>
+        <v>39.20875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5233</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2179</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3055</v>
+      </c>
+      <c r="F75" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1802</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>104</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1906</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1524</v>
+      </c>
+      <c r="L75" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="M75" t="n">
+        <v>9.525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>56.695</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.020000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2410215482841183</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.080000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01816652649285122</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.331334332833583</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.07999999999999829</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.001372448104306034</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
